--- a/08.advanced-analytics-stats/data/GB_Shared.xlsx
+++ b/08.advanced-analytics-stats/data/GB_Shared.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sudeep Bhargava\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253AABF1-29DD-4AEA-A3AD-D3C949C7EC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0683A15-E435-4CAE-A8F1-A6AF6906FAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{790EC4C7-9592-45C6-B729-56D738E523FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{790EC4C7-9592-45C6-B729-56D738E523FA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Continuous" sheetId="1" r:id="rId1"/>
-    <sheet name="Categorical" sheetId="2" r:id="rId2"/>
+    <sheet name="Continuous_GB" sheetId="1" r:id="rId1"/>
+    <sheet name="Continuous_XGB" sheetId="3" r:id="rId2"/>
+    <sheet name="Continuous_AdaBoost" sheetId="5" r:id="rId3"/>
+    <sheet name="Categorical_GB" sheetId="2" r:id="rId4"/>
+    <sheet name="Categorical_XGB" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="95">
   <si>
     <t>x</t>
   </si>
@@ -170,12 +173,166 @@
   </si>
   <si>
     <t>New probability for the right node</t>
+  </si>
+  <si>
+    <t>Prob1</t>
+  </si>
+  <si>
+    <t>Considering the same split for the second iteration</t>
+  </si>
+  <si>
+    <t>NewProb for the left node</t>
+  </si>
+  <si>
+    <t>NewProb for the right node</t>
+  </si>
+  <si>
+    <t>Prob2</t>
+  </si>
+  <si>
+    <t>Avg of all responses</t>
+  </si>
+  <si>
+    <t>pred1</t>
+  </si>
+  <si>
+    <t>grad1</t>
+  </si>
+  <si>
+    <t>hessian1</t>
+  </si>
+  <si>
+    <t>Assume the first split at x&lt;=5</t>
+  </si>
+  <si>
+    <t>Total gradient for left node</t>
+  </si>
+  <si>
+    <t>Total hhessian for left node</t>
+  </si>
+  <si>
+    <t>Total gradient for right node</t>
+  </si>
+  <si>
+    <t>Total hhessian for right node</t>
+  </si>
+  <si>
+    <t>Left leaf value</t>
+  </si>
+  <si>
+    <t>Right leaf value</t>
+  </si>
+  <si>
+    <t>1 has been added as a value for lambda, which is a hyperparameter used to avoid overfitting</t>
+  </si>
+  <si>
+    <t>New predictions</t>
+  </si>
+  <si>
+    <t>left node</t>
+  </si>
+  <si>
+    <t>right node</t>
+  </si>
+  <si>
+    <t>pred2</t>
+  </si>
+  <si>
+    <t>grad2</t>
+  </si>
+  <si>
+    <t>hessian2</t>
+  </si>
+  <si>
+    <t>Assume the split to be the same x&lt;=5</t>
+  </si>
+  <si>
+    <t>New prediction</t>
+  </si>
+  <si>
+    <t>Base Probability</t>
+  </si>
+  <si>
+    <t>(3/8)</t>
+  </si>
+  <si>
+    <t>Base odds ratio</t>
+  </si>
+  <si>
+    <t>Log of base odds ratio</t>
+  </si>
+  <si>
+    <t>gradient1</t>
+  </si>
+  <si>
+    <t>Assume the split to be x&lt;=5</t>
+  </si>
+  <si>
+    <t>Prediction for new logit</t>
+  </si>
+  <si>
+    <t>Left leaf</t>
+  </si>
+  <si>
+    <t>Right leaf</t>
+  </si>
+  <si>
+    <t>Prediction for new probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step#1 </t>
+  </si>
+  <si>
+    <t>Assign equal weights to all rows</t>
+  </si>
+  <si>
+    <t>(1/number of rows)</t>
+  </si>
+  <si>
+    <t>Decide upon an appropriate split. Here we consider it as  x&lt;=5</t>
+  </si>
+  <si>
+    <t>Average for each split</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>error/max</t>
+  </si>
+  <si>
+    <t>error/max*wt</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>log((1-0.479)/0.479))</t>
+  </si>
+  <si>
+    <t>(L)</t>
+  </si>
+  <si>
+    <t>NewWt</t>
+  </si>
+  <si>
+    <t>NormalizedNewWt</t>
+  </si>
+  <si>
+    <t>low_bin</t>
+  </si>
+  <si>
+    <t>upper_bin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -211,10 +368,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -230,6 +390,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>20053</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>237677</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>23584</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBEC1919-57FE-4F03-AC12-C4E635E570DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4277895" y="4999790"/>
+          <a:ext cx="2042414" cy="798952"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1615,8 +1824,1775 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCF6BF5-7F88-459B-AF5A-9DAA8942F5F5}">
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <f>AVERAGE(B2:B11)</f>
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <f>$F$11</f>
+        <v>13.4</v>
+      </c>
+      <c r="D15">
+        <f>C15-B15</f>
+        <v>8.4</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ref="C16:C24" si="0">$F$11</f>
+        <v>13.4</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ref="D16:D24" si="1">C16-B16</f>
+        <v>7.4</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>13.4</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>6.4</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>13.4</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>13.4</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>6</v>
+      </c>
+      <c r="B20">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>13.4</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>-0.59999999999999964</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>7</v>
+      </c>
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>13.4</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>-2.5999999999999996</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>8</v>
+      </c>
+      <c r="B22">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>13.4</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>-5.6</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>9</v>
+      </c>
+      <c r="B23">
+        <v>23</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>13.4</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>-9.6</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>10</v>
+      </c>
+      <c r="B24">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>13.4</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>-11.6</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28">
+        <f>SUM(D15:D19)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29">
+        <f>5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31">
+        <f>SUM(D20:D24)</f>
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34">
+        <f>-D28/(D29+1)</f>
+        <v>-5</v>
+      </c>
+      <c r="F34" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D34)</f>
+        <v>=-D28/(D29+1)</v>
+      </c>
+      <c r="H34" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35">
+        <f>-D31/(D32+1)</f>
+        <v>5</v>
+      </c>
+      <c r="H35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39">
+        <f>F11+0.1*D34</f>
+        <v>12.9</v>
+      </c>
+      <c r="F39" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D39)</f>
+        <v>=F11+0.1*D34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40">
+        <f>F11+0.1*D35</f>
+        <v>13.9</v>
+      </c>
+      <c r="F40" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D40)</f>
+        <v>=F11+0.1*D35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" t="s">
+        <v>65</v>
+      </c>
+      <c r="G42" t="s">
+        <v>66</v>
+      </c>
+      <c r="H42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43">
+        <v>5</v>
+      </c>
+      <c r="C43">
+        <f>$F$11</f>
+        <v>13.4</v>
+      </c>
+      <c r="D43">
+        <f>C43-B43</f>
+        <v>8.4</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <f>$D$39</f>
+        <v>12.9</v>
+      </c>
+      <c r="G43">
+        <f>F43-B43</f>
+        <v>7.9</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44">
+        <v>6</v>
+      </c>
+      <c r="C44">
+        <f t="shared" ref="C44:C52" si="2">$F$11</f>
+        <v>13.4</v>
+      </c>
+      <c r="D44">
+        <f t="shared" ref="D44:D52" si="3">C44-B44</f>
+        <v>7.4</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <f t="shared" ref="F44:F47" si="4">$D$39</f>
+        <v>12.9</v>
+      </c>
+      <c r="G44">
+        <f t="shared" ref="G44:G52" si="5">F44-B44</f>
+        <v>6.9</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="3"/>
+        <v>6.4</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="4"/>
+        <v>12.9</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="5"/>
+        <v>5.9</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>4</v>
+      </c>
+      <c r="B46">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="4"/>
+        <v>12.9</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="5"/>
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>5</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="3"/>
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="4"/>
+        <v>12.9</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="5"/>
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>6</v>
+      </c>
+      <c r="B48">
+        <v>14</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="3"/>
+        <v>-0.59999999999999964</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <f>$D$40</f>
+        <v>13.9</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="5"/>
+        <v>-9.9999999999999645E-2</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>7</v>
+      </c>
+      <c r="B49">
+        <v>16</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="3"/>
+        <v>-2.5999999999999996</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <f t="shared" ref="F49:F52" si="6">$D$40</f>
+        <v>13.9</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="5"/>
+        <v>-2.0999999999999996</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>8</v>
+      </c>
+      <c r="B50">
+        <v>19</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="3"/>
+        <v>-5.6</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="6"/>
+        <v>13.9</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="5"/>
+        <v>-5.0999999999999996</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>9</v>
+      </c>
+      <c r="B51">
+        <v>23</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="3"/>
+        <v>-9.6</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="6"/>
+        <v>13.9</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="5"/>
+        <v>-9.1</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>10</v>
+      </c>
+      <c r="B52">
+        <v>25</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="3"/>
+        <v>-11.6</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="6"/>
+        <v>13.9</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="5"/>
+        <v>-11.1</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>7.9</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>-9.9999999999999645E-2</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>6.9</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>-2.0999999999999996</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>5.9</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>-5.0999999999999996</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>-9.1</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>-11.1</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <f>-SUM(A56:A60)/(SUM(B56:B60)+1)</f>
+        <v>-4.583333333333333</v>
+      </c>
+      <c r="D62">
+        <f>-SUM(D56:D60)/(SUM(E56:E60)+1)</f>
+        <v>4.583333333333333</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(A62)</f>
+        <v>=-SUM(A56:A60)/(SUM(B56:B60)+1)</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="3">
+        <f>D39+0.1*A62</f>
+        <v>12.441666666666666</v>
+      </c>
+      <c r="E66" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C66)</f>
+        <v>=D39+0.1*A62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="3">
+        <f>D40+0.1*D62</f>
+        <v>14.358333333333334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3CAF9A-E699-454F-9F10-EA4170C3B5F8}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13">
+        <f>1/10</f>
+        <v>0.1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>7</v>
+      </c>
+      <c r="B19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>9</v>
+      </c>
+      <c r="B20">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f>AVERAGE(A17:A21)</f>
+        <v>7.4</v>
+      </c>
+      <c r="B22">
+        <f>AVERAGE(B17:B21)</f>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <f>$A$22</f>
+        <v>7.4</v>
+      </c>
+      <c r="D25">
+        <f>ABS(B25-C25)</f>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="E25" s="4">
+        <f>D25/MAX($D$25:$D$34)</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="F25" s="4">
+        <f>E25*$F$13</f>
+        <v>4.2857142857142858E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ref="C26:C29" si="0">$A$22</f>
+        <v>7.4</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ref="D26:D34" si="1">ABS(B26-C26)</f>
+        <v>1.4000000000000004</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" ref="E26:E34" si="2">D26/MAX($D$25:$D$34)</f>
+        <v>0.25</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" ref="F26:F34" si="3">E26*$F$13</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>7.4</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="1"/>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" si="2"/>
+        <v>7.142857142857148E-2</v>
+      </c>
+      <c r="F27" s="4">
+        <f t="shared" si="3"/>
+        <v>7.1428571428571487E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>7.4</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="1"/>
+        <v>1.5999999999999996</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="2"/>
+        <v>0.28571428571428559</v>
+      </c>
+      <c r="F28" s="4">
+        <f>E28*$F$13</f>
+        <v>2.857142857142856E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <v>10</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>7.4</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="1"/>
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="E29" s="4">
+        <f t="shared" si="2"/>
+        <v>0.46428571428571408</v>
+      </c>
+      <c r="F29" s="4">
+        <f t="shared" si="3"/>
+        <v>4.6428571428571409E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30">
+        <f>$B$22</f>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="1"/>
+        <v>5.3999999999999986</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="2"/>
+        <v>0.96428571428571375</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="3"/>
+        <v>9.6428571428571377E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>7</v>
+      </c>
+      <c r="B31">
+        <v>16</v>
+      </c>
+      <c r="C31">
+        <f t="shared" ref="C31:C34" si="4">$B$22</f>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="1"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="E31" s="4">
+        <f t="shared" si="2"/>
+        <v>0.60714285714285676</v>
+      </c>
+      <c r="F31" s="4">
+        <f t="shared" si="3"/>
+        <v>6.0714285714285679E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>8</v>
+      </c>
+      <c r="B32">
+        <v>19</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="4"/>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="1"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" si="2"/>
+        <v>7.1428571428571161E-2</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="3"/>
+        <v>7.1428571428571166E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>23</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="4"/>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="1"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="E33" s="4">
+        <f t="shared" si="2"/>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="F33" s="4">
+        <f>E33*$F$13</f>
+        <v>6.4285714285714293E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>10</v>
+      </c>
+      <c r="B34">
+        <v>25</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="4"/>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="1"/>
+        <v>5.6000000000000014</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F35" s="5">
+        <f>SUM(F25:F34)</f>
+        <v>0.47857142857142843</v>
+      </c>
+      <c r="G35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="5">
+        <f>LOG((1-F35)/F35,2.7183)</f>
+        <v>8.5766248417431995E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" t="s">
+        <v>86</v>
+      </c>
+      <c r="F39" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" t="s">
+        <v>91</v>
+      </c>
+      <c r="H39" t="s">
+        <v>92</v>
+      </c>
+      <c r="J39" t="s">
+        <v>93</v>
+      </c>
+      <c r="K39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40">
+        <v>5</v>
+      </c>
+      <c r="C40">
+        <f>$A$22</f>
+        <v>7.4</v>
+      </c>
+      <c r="D40">
+        <f>ABS(B40-C40)</f>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="E40" s="4">
+        <f>D40/MAX($D$25:$D$34)</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="F40" s="4">
+        <f>E40*$F$13</f>
+        <v>4.2857142857142858E-2</v>
+      </c>
+      <c r="G40">
+        <f>0.1*2.7183^($E$36*E40)</f>
+        <v>0.10374411092309135</v>
+      </c>
+      <c r="H40">
+        <f>G40/$G$50</f>
+        <v>9.953627208537609E-2</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <f>J40+H40</f>
+        <v>9.953627208537609E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:C44" si="5">$A$22</f>
+        <v>7.4</v>
+      </c>
+      <c r="D41">
+        <f t="shared" ref="D41:D49" si="6">ABS(B41-C41)</f>
+        <v>1.4000000000000004</v>
+      </c>
+      <c r="E41" s="4">
+        <f t="shared" ref="E41:E49" si="7">D41/MAX($D$25:$D$34)</f>
+        <v>0.25</v>
+      </c>
+      <c r="F41" s="4">
+        <f t="shared" ref="F41:F49" si="8">E41*$F$13</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G41">
+        <f t="shared" ref="G41:G49" si="9">0.1*2.7183^($E$36*E41)</f>
+        <v>0.10216732306092952</v>
+      </c>
+      <c r="H41">
+        <f t="shared" ref="H41:H49" si="10">G41/$G$50</f>
+        <v>9.8023438399949758E-2</v>
+      </c>
+      <c r="J41">
+        <f>K40</f>
+        <v>9.953627208537609E-2</v>
+      </c>
+      <c r="K41">
+        <f>J41+H41</f>
+        <v>0.19755971048532583</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="5"/>
+        <v>7.4</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="6"/>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="E42" s="4">
+        <f t="shared" si="7"/>
+        <v>7.142857142857148E-2</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="8"/>
+        <v>7.1428571428571487E-3</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="9"/>
+        <v>0.10061450051053467</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="10"/>
+        <v>9.6533597998396836E-2</v>
+      </c>
+      <c r="J42">
+        <f t="shared" ref="J42:J49" si="11">K41</f>
+        <v>0.19755971048532583</v>
+      </c>
+      <c r="K42">
+        <f t="shared" ref="K42:K49" si="12">J42+H42</f>
+        <v>0.29409330848372267</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>4</v>
+      </c>
+      <c r="B43">
+        <v>9</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="5"/>
+        <v>7.4</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="6"/>
+        <v>1.5999999999999996</v>
+      </c>
+      <c r="E43" s="4">
+        <f t="shared" si="7"/>
+        <v>0.28571428571428559</v>
+      </c>
+      <c r="F43" s="4">
+        <f t="shared" si="8"/>
+        <v>2.857142857142856E-2</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="9"/>
+        <v>0.10248075165420628</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="10"/>
+        <v>9.8324154396859306E-2</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="11"/>
+        <v>0.29409330848372267</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="12"/>
+        <v>0.39241746288058199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>5</v>
+      </c>
+      <c r="B44">
+        <v>10</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="5"/>
+        <v>7.4</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="6"/>
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="E44" s="4">
+        <f t="shared" si="7"/>
+        <v>0.46428571428571408</v>
+      </c>
+      <c r="F44" s="4">
+        <f t="shared" si="8"/>
+        <v>4.6428571428571409E-2</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="9"/>
+        <v>0.10406237678122664</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="10"/>
+        <v>9.9841629148721342E-2</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="11"/>
+        <v>0.39241746288058199</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="12"/>
+        <v>0.49225909202930335</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>6</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45">
+        <f>$B$22</f>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="6"/>
+        <v>5.3999999999999986</v>
+      </c>
+      <c r="E45" s="4">
+        <f t="shared" si="7"/>
+        <v>0.96428571428571375</v>
+      </c>
+      <c r="F45" s="4">
+        <f t="shared" si="8"/>
+        <v>9.6428571428571377E-2</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="9"/>
+        <v>0.10862199366907133</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="10"/>
+        <v>0.10421630895575189</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="11"/>
+        <v>0.49225909202930335</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="12"/>
+        <v>0.59647540098505525</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>7</v>
+      </c>
+      <c r="B46">
+        <v>16</v>
+      </c>
+      <c r="C46">
+        <f t="shared" ref="C46:C49" si="13">$B$22</f>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="6"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="E46" s="4">
+        <f t="shared" si="7"/>
+        <v>0.60714285714285676</v>
+      </c>
+      <c r="F46" s="4">
+        <f t="shared" si="8"/>
+        <v>6.0714285714285679E-2</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="9"/>
+        <v>0.10534523396295747</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="10"/>
+        <v>0.10107245391893023</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="11"/>
+        <v>0.59647540098505525</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="12"/>
+        <v>0.69754785490398552</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>8</v>
+      </c>
+      <c r="B47">
+        <v>19</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="13"/>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="6"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="E47" s="4">
+        <f t="shared" si="7"/>
+        <v>7.1428571428571161E-2</v>
+      </c>
+      <c r="F47" s="4">
+        <f t="shared" si="8"/>
+        <v>7.1428571428571166E-3</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="9"/>
+        <v>0.10061450051053467</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="10"/>
+        <v>9.6533597998396836E-2</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="11"/>
+        <v>0.69754785490398552</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="12"/>
+        <v>0.7940814529023823</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>9</v>
+      </c>
+      <c r="B48">
+        <v>23</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="13"/>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="6"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="7"/>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="F48" s="4">
+        <f>E48*$F$13</f>
+        <v>6.4285714285714293E-2</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="9"/>
+        <v>0.10566841174133315</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="10"/>
+        <v>0.10138252367608683</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="11"/>
+        <v>0.7940814529023823</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="12"/>
+        <v>0.8954639765784691</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>10</v>
+      </c>
+      <c r="B49">
+        <v>25</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="13"/>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="6"/>
+        <v>5.6000000000000014</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="8"/>
+        <v>0.1</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="9"/>
+        <v>0.10895522388059709</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="10"/>
+        <v>0.10453602342153091</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="11"/>
+        <v>0.8954639765784691</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F50" s="4">
+        <f>SUM(F40:F49)</f>
+        <v>0.47857142857142843</v>
+      </c>
+      <c r="G50">
+        <f>SUM(G40:G49)</f>
+        <v>1.0422744266944821</v>
+      </c>
+      <c r="H50">
+        <f>SUM(H40:H49)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93C7876-47E6-4759-9136-26166318F87A}">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -2045,6 +4021,1032 @@
         <v>=1/(1+2.7183^-A41)</v>
       </c>
     </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>1</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <f>$F$11</f>
+        <v>0.375</v>
+      </c>
+      <c r="D49">
+        <f>B49-C49</f>
+        <v>-0.375</v>
+      </c>
+      <c r="E49">
+        <f>$A$44</f>
+        <v>0.33831175504726491</v>
+      </c>
+      <c r="F49">
+        <f>B49-E49</f>
+        <v>-0.33831175504726491</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>2</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <f t="shared" ref="C50:C56" si="3">$F$11</f>
+        <v>0.375</v>
+      </c>
+      <c r="D50">
+        <f t="shared" ref="D50:D56" si="4">B50-C50</f>
+        <v>-0.375</v>
+      </c>
+      <c r="E50">
+        <f t="shared" ref="E50:E52" si="5">$A$44</f>
+        <v>0.33831175504726491</v>
+      </c>
+      <c r="F50">
+        <f t="shared" ref="F50:F56" si="6">B50-E50</f>
+        <v>-0.33831175504726491</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>3</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="4"/>
+        <v>-0.375</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="5"/>
+        <v>0.33831175504726491</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="6"/>
+        <v>-0.33831175504726491</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="4"/>
+        <v>-0.375</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="5"/>
+        <v>0.33831175504726491</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="6"/>
+        <v>-0.33831175504726491</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>5</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="4"/>
+        <v>-0.375</v>
+      </c>
+      <c r="E53">
+        <f>$A$46</f>
+        <v>0.41318248313309863</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="6"/>
+        <v>-0.41318248313309863</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>6</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="4"/>
+        <v>0.625</v>
+      </c>
+      <c r="E54">
+        <f t="shared" ref="E54:E56" si="7">$A$46</f>
+        <v>0.41318248313309863</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="6"/>
+        <v>0.58681751686690142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>7</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="4"/>
+        <v>0.625</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="7"/>
+        <v>0.41318248313309863</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="6"/>
+        <v>0.58681751686690142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="4"/>
+        <v>0.625</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="7"/>
+        <v>0.41318248313309863</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="6"/>
+        <v>0.58681751686690142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>-0.33831175504726491</v>
+      </c>
+      <c r="B61">
+        <v>-0.41318248313309863</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>-0.33831175504726491</v>
+      </c>
+      <c r="B62">
+        <v>0.58681751686690142</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>-0.33831175504726491</v>
+      </c>
+      <c r="B63">
+        <v>0.58681751686690142</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>-0.33831175504726491</v>
+      </c>
+      <c r="B64">
+        <v>0.58681751686690142</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <f>SUM(A61:A64)/(4*E49*(1-E49))</f>
+        <v>-1.5112857265152577</v>
+      </c>
+      <c r="B65">
+        <f>SUM(B61:B64)/(4*E53*(1-E53))</f>
+        <v>1.3891517779822529</v>
+      </c>
+      <c r="C65" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <f>A39+0.1*A65</f>
+        <v>-0.82195078161498658</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <f>A41+0.1*B65</f>
+        <v>-0.21190703116523543</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <f>1/(1+2.7183^-A68)</f>
+        <v>0.30534855459872906</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <f>1/(1+2.7183^-A70)</f>
+        <v>0.44722024747222405</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" t="s">
+        <v>5</v>
+      </c>
+      <c r="E77" t="s">
+        <v>45</v>
+      </c>
+      <c r="F77" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" t="s">
+        <v>49</v>
+      </c>
+      <c r="H77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>1</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <f>$F$11</f>
+        <v>0.375</v>
+      </c>
+      <c r="D78">
+        <f>B78-C78</f>
+        <v>-0.375</v>
+      </c>
+      <c r="E78">
+        <f>$A$44</f>
+        <v>0.33831175504726491</v>
+      </c>
+      <c r="F78">
+        <f>B78-E78</f>
+        <v>-0.33831175504726491</v>
+      </c>
+      <c r="G78">
+        <f>$A$73</f>
+        <v>0.30534855459872906</v>
+      </c>
+      <c r="H78">
+        <f>B78-G78</f>
+        <v>-0.30534855459872906</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>2</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <f t="shared" ref="C79:C85" si="8">$F$11</f>
+        <v>0.375</v>
+      </c>
+      <c r="D79">
+        <f t="shared" ref="D79:D85" si="9">B79-C79</f>
+        <v>-0.375</v>
+      </c>
+      <c r="E79">
+        <f t="shared" ref="E79:E81" si="10">$A$44</f>
+        <v>0.33831175504726491</v>
+      </c>
+      <c r="F79">
+        <f t="shared" ref="F79:F85" si="11">B79-E79</f>
+        <v>-0.33831175504726491</v>
+      </c>
+      <c r="G79">
+        <f t="shared" ref="G79:G81" si="12">$A$73</f>
+        <v>0.30534855459872906</v>
+      </c>
+      <c r="H79">
+        <f t="shared" ref="H79:H85" si="13">B79-G79</f>
+        <v>-0.30534855459872906</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>3</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="8"/>
+        <v>0.375</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="9"/>
+        <v>-0.375</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="10"/>
+        <v>0.33831175504726491</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="11"/>
+        <v>-0.33831175504726491</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="12"/>
+        <v>0.30534855459872906</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="13"/>
+        <v>-0.30534855459872906</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>4</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="8"/>
+        <v>0.375</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="9"/>
+        <v>-0.375</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="10"/>
+        <v>0.33831175504726491</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="11"/>
+        <v>-0.33831175504726491</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="12"/>
+        <v>0.30534855459872906</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="13"/>
+        <v>-0.30534855459872906</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>5</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="8"/>
+        <v>0.375</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="9"/>
+        <v>-0.375</v>
+      </c>
+      <c r="E82">
+        <f>$A$46</f>
+        <v>0.41318248313309863</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="11"/>
+        <v>-0.41318248313309863</v>
+      </c>
+      <c r="G82">
+        <f>$A$75</f>
+        <v>0.44722024747222405</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="13"/>
+        <v>-0.44722024747222405</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="8"/>
+        <v>0.375</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="9"/>
+        <v>0.625</v>
+      </c>
+      <c r="E83">
+        <f t="shared" ref="E83:E85" si="14">$A$46</f>
+        <v>0.41318248313309863</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="11"/>
+        <v>0.58681751686690142</v>
+      </c>
+      <c r="G83">
+        <f t="shared" ref="G83:G85" si="15">$A$75</f>
+        <v>0.44722024747222405</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="13"/>
+        <v>0.552779752527776</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>7</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="8"/>
+        <v>0.375</v>
+      </c>
+      <c r="D84">
+        <f t="shared" si="9"/>
+        <v>0.625</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="14"/>
+        <v>0.41318248313309863</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="11"/>
+        <v>0.58681751686690142</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="15"/>
+        <v>0.44722024747222405</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="13"/>
+        <v>0.552779752527776</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>8</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="8"/>
+        <v>0.375</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="9"/>
+        <v>0.625</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="14"/>
+        <v>0.41318248313309863</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="11"/>
+        <v>0.58681751686690142</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="15"/>
+        <v>0.44722024747222405</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="13"/>
+        <v>0.552779752527776</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86940995-16BE-41ED-80A6-696F73B6CE64}">
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11">
+        <f>3/8</f>
+        <v>0.375</v>
+      </c>
+      <c r="E11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12">
+        <f>D11/(1-D11)</f>
+        <v>0.6</v>
+      </c>
+      <c r="E12" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D12)</f>
+        <v>=D11/(1-D11)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13">
+        <f>LOG(D12,2.7183)</f>
+        <v>-0.51082220896346076</v>
+      </c>
+      <c r="E13" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D13)</f>
+        <v>=LOG(D12,2.7183)</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <f>$D$11</f>
+        <v>0.375</v>
+      </c>
+      <c r="D16">
+        <f>C16-B16</f>
+        <v>0.375</v>
+      </c>
+      <c r="E16">
+        <f>$D$11*(1-$D$11)</f>
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <f t="shared" ref="C17:C23" si="0">$D$11</f>
+        <v>0.375</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ref="D17:D23" si="1">C17-B17</f>
+        <v>0.375</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ref="E17:E23" si="2">$D$11*(1-$D$11)</f>
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>-0.625</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>-0.625</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="2"/>
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>-0.625</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="2"/>
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>0.375</v>
+      </c>
+      <c r="B27">
+        <v>0.234375</v>
+      </c>
+      <c r="D27">
+        <v>-0.625</v>
+      </c>
+      <c r="E27">
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>0.375</v>
+      </c>
+      <c r="B28">
+        <v>0.234375</v>
+      </c>
+      <c r="D28">
+        <v>-0.625</v>
+      </c>
+      <c r="E28">
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>0.375</v>
+      </c>
+      <c r="B29">
+        <v>0.234375</v>
+      </c>
+      <c r="D29">
+        <v>-0.625</v>
+      </c>
+      <c r="E29">
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>0.375</v>
+      </c>
+      <c r="B30">
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>0.375</v>
+      </c>
+      <c r="B31">
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <f>-SUM(A27:A31)/(SUM(B27:B31)+1)</f>
+        <v>-0.86330935251798557</v>
+      </c>
+      <c r="D33">
+        <f>-SUM(D27:D29)/(SUM(E27:E29)+1)</f>
+        <v>1.1009174311926606</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(A33)</f>
+        <v>=-SUM(A27:A31)/(SUM(B27:B31)+1)</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37">
+        <f>D13+0.1*A33</f>
+        <v>-0.59715314421525933</v>
+      </c>
+      <c r="D37" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B37)</f>
+        <v>=D13+0.1*A33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38">
+        <f>D13+0.1*D33</f>
+        <v>-0.40073046584419469</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41">
+        <f>1/(1+2.7183^-B37)</f>
+        <v>0.35499436521730826</v>
+      </c>
+      <c r="D41" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B41)</f>
+        <v>=1/(1+2.7183^-B37)</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42">
+        <f>1/(1+2.7183^-B38)</f>
+        <v>0.40113620674843059</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
